--- a/docs/reports/连通标注_2026-07-04_分表/7_关键舆论平台.xlsx
+++ b/docs/reports/连通标注_2026-07-04_分表/7_关键舆论平台.xlsx
@@ -1458,7 +1458,7 @@
       </c>
       <c r="K3" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -1516,7 +1516,7 @@
       </c>
       <c r="K4" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -1574,7 +1574,7 @@
       </c>
       <c r="K5" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1632,12 +1632,12 @@
       </c>
       <c r="K6" s="183" t="inlineStr">
         <is>
-          <t>⚠️ 联通但为空</t>
+          <t>⚠️ 联通·暂无数据</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>请求成功但解析出 0 条(feed 为空或格式不符)</t>
+          <t>请求成功但当前无内容</t>
         </is>
       </c>
     </row>
@@ -1690,12 +1690,12 @@
       </c>
       <c r="K7" s="183" t="inlineStr">
         <is>
-          <t>⚠️ 联通但为空</t>
+          <t>⚠️ 联通·暂无数据</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>请求成功但解析出 0 条(feed 为空或格式不符)</t>
+          <t>请求成功但当前无内容</t>
         </is>
       </c>
     </row>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="K8" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>HTTP 403,反爬/拒绝访问</t>
+          <t>HTTP 403,访问被拒</t>
         </is>
       </c>
     </row>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="K9" s="183" t="inlineStr">
         <is>
-          <t>⚠️ 联通但为空</t>
+          <t>⚠️ 联通·暂无数据</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>请求成功但解析出 0 条(feed 为空或格式不符)</t>
+          <t>请求成功但当前无内容</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="K10" s="183" t="inlineStr">
         <is>
-          <t>⚠️ 联通但为空</t>
+          <t>⚠️ 联通·暂无数据</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>请求成功但解析出 0 条(feed 为空或格式不符)</t>
+          <t>请求成功但当前无内容</t>
         </is>
       </c>
     </row>
@@ -1922,12 +1922,12 @@
       </c>
       <c r="K11" s="183" t="inlineStr">
         <is>
-          <t>⚠️ 联通但为空</t>
+          <t>⚠️ 联通·暂无数据</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>请求成功但解析出 0 条(feed 为空或格式不符)</t>
+          <t>请求成功但当前无内容</t>
         </is>
       </c>
     </row>
@@ -1980,7 +1980,7 @@
       </c>
       <c r="K12" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -2038,7 +2038,7 @@
       </c>
       <c r="K13" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="K14" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -2154,7 +2154,7 @@
       </c>
       <c r="K15" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -2212,7 +2212,7 @@
       </c>
       <c r="K16" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="K17" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2328,7 +2328,7 @@
       </c>
       <c r="K18" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="K19" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="K20" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2502,7 +2502,7 @@
       </c>
       <c r="K21" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2560,7 +2560,7 @@
       </c>
       <c r="K22" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="K23" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2676,7 +2676,7 @@
       </c>
       <c r="K24" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="K25" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2792,7 +2792,7 @@
       </c>
       <c r="K26" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2850,7 +2850,7 @@
       </c>
       <c r="K27" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2908,7 +2908,7 @@
       </c>
       <c r="K28" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="K29" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="K30" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -3082,7 +3082,7 @@
       </c>
       <c r="K31" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -3140,7 +3140,7 @@
       </c>
       <c r="K32" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -3198,7 +3198,7 @@
       </c>
       <c r="K33" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -3256,7 +3256,7 @@
       </c>
       <c r="K34" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="K35" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -3372,7 +3372,7 @@
       </c>
       <c r="K36" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="K37" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -3488,7 +3488,7 @@
       </c>
       <c r="K38" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -3546,7 +3546,7 @@
       </c>
       <c r="K39" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -3604,7 +3604,7 @@
       </c>
       <c r="K40" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -3662,7 +3662,7 @@
       </c>
       <c r="K41" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3720,7 +3720,7 @@
       </c>
       <c r="K42" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3776,14 +3776,14 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="K43" s="185" t="inlineStr">
-        <is>
-          <t>🔌 待开发插件</t>
+      <c r="K43" s="182" t="inlineStr">
+        <is>
+          <t>🟢 联通·免费</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>无 公开API provider 插件</t>
+          <t>验证:接口/官网可达(HTTP 200);经API取数</t>
         </is>
       </c>
     </row>
@@ -3834,14 +3834,14 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="K44" s="185" t="inlineStr">
-        <is>
-          <t>🔌 待开发插件</t>
+      <c r="K44" s="182" t="inlineStr">
+        <is>
+          <t>🟢 联通·免费</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>无 Bluesky API provider 插件</t>
+          <t>验证:接口/官网可达(HTTP 200);经API取数</t>
         </is>
       </c>
     </row>
